--- a/2025/Factures ventes enregistrées VC CONVENTION EDC.xlsx
+++ b/2025/Factures ventes enregistrées VC CONVENTION EDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/dashbord convention/table vente/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE5C3833-E6A6-4D97-A6F1-F51CE4DA4596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4FA1F81-01DC-4975-B653-7763486D23E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/2025/Factures ventes enregistrées VC CONVENTION EDC.xlsx
+++ b/2025/Factures ventes enregistrées VC CONVENTION EDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/dashbord convention/table vente/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC76DCFA-D028-4649-ADBE-5A57F3A7224A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10ED549F-B1B8-401B-9953-99A16F6ECC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/2025/Factures ventes enregistrées VC CONVENTION EDC.xlsx
+++ b/2025/Factures ventes enregistrées VC CONVENTION EDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/dashbord convention/table vente/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4A49019-8883-4377-8E37-7FA7C8EBC08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22810D82-F560-49E4-B2A7-81A766A08B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
